--- a/src/main/resources/python/MultifacetedModeling/DataOutput/SVR/avg_classes.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/DataOutput/SVR/avg_classes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,88 +455,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.06299551458842</t>
+          <t>0.0609620922024863</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.05177768241353431</t>
+          <t>0.0351276875056667</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9599856978345308</t>
+          <t>0.9817229306572706</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.06539193208937237</t>
+          <t>0.06407048895718997</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.05959137913363234</t>
+          <t>0.05298650512111957</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9473404571396604</t>
+          <t>0.958306373637564</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.06283983126097245</t>
+          <t>0.0656603977897534</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0694596904573526</t>
+          <t>0.05872798808498908</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9284634809300553</t>
+          <t>0.948829420366232</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0.06569338253350683</t>
+          <t>0.06342587053483276</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.05390273725855973</t>
+          <t>0.06863570118285497</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9569014582386844</t>
+          <t>0.930123645730907</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
     </row>
